--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/80.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/80.xlsx
@@ -426,13 +426,13 @@
         <v>-1.933444641734644</v>
       </c>
       <c r="E2">
-        <v>-8.413105243059768</v>
+        <v>-3.189202538979489</v>
       </c>
       <c r="F2">
-        <v>-3.056623676431307</v>
+        <v>-1.849369307265336</v>
       </c>
       <c r="G2">
-        <v>-11.23433058040428</v>
+        <v>-8.756375027262546</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-1.403345323929236</v>
       </c>
       <c r="E3">
-        <v>-8.144793158105299</v>
+        <v>-4.443309073715703</v>
       </c>
       <c r="F3">
-        <v>-2.861707998185181</v>
+        <v>-1.570651012347594</v>
       </c>
       <c r="G3">
-        <v>-11.48009407520669</v>
+        <v>-9.095131622281178</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-0.9281224298943161</v>
       </c>
       <c r="E4">
-        <v>-8.832767986298595</v>
+        <v>-4.975472696727085</v>
       </c>
       <c r="F4">
-        <v>-2.919452661466931</v>
+        <v>-1.648553168009068</v>
       </c>
       <c r="G4">
-        <v>-11.62819529151379</v>
+        <v>-8.851244986210771</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-0.5856174410222756</v>
       </c>
       <c r="E5">
-        <v>-9.685869090707584</v>
+        <v>-5.911408647684379</v>
       </c>
       <c r="F5">
-        <v>-2.797549286103553</v>
+        <v>-1.759352278337919</v>
       </c>
       <c r="G5">
-        <v>-11.21443653408937</v>
+        <v>-8.70163112676477</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-0.349724717784743</v>
       </c>
       <c r="E6">
-        <v>-9.961807125890969</v>
+        <v>-6.885660017220572</v>
       </c>
       <c r="F6">
-        <v>-2.575738175023333</v>
+        <v>-1.653248354448136</v>
       </c>
       <c r="G6">
-        <v>-11.73412952956046</v>
+        <v>-7.693203461235948</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-0.2170780829474187</v>
       </c>
       <c r="E7">
-        <v>-10.92424370674115</v>
+        <v>-7.723033731400921</v>
       </c>
       <c r="F7">
-        <v>-2.71377069208662</v>
+        <v>-1.674587098744251</v>
       </c>
       <c r="G7">
-        <v>-12.09126096531198</v>
+        <v>-7.787367957548892</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-0.1615933672301416</v>
       </c>
       <c r="E8">
-        <v>-11.54139772992849</v>
+        <v>-8.080035979795614</v>
       </c>
       <c r="F8">
-        <v>-2.527048395821583</v>
+        <v>-1.200537285144178</v>
       </c>
       <c r="G8">
-        <v>-12.07233816057866</v>
+        <v>-8.232081759165112</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-0.1560627099793794</v>
       </c>
       <c r="E9">
-        <v>-12.91141055689103</v>
+        <v>-8.717903243094037</v>
       </c>
       <c r="F9">
-        <v>-2.24718446878577</v>
+        <v>-1.277277241339524</v>
       </c>
       <c r="G9">
-        <v>-11.72928644653872</v>
+        <v>-8.47803884603953</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-0.1614503529604252</v>
       </c>
       <c r="E10">
-        <v>-12.92717417491173</v>
+        <v>-9.801354234851193</v>
       </c>
       <c r="F10">
-        <v>-2.510510868992094</v>
+        <v>-1.452037912308136</v>
       </c>
       <c r="G10">
-        <v>-11.7641592692725</v>
+        <v>-8.028869145545583</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-0.1403369271048954</v>
       </c>
       <c r="E11">
-        <v>-12.60312110339684</v>
+        <v>-11.04164439539</v>
       </c>
       <c r="F11">
-        <v>-1.970759094838978</v>
+        <v>-1.21494507938107</v>
       </c>
       <c r="G11">
-        <v>-10.57281662669087</v>
+        <v>-6.809449090079786</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-0.05521118488984757</v>
       </c>
       <c r="E12">
-        <v>-14.37168492777445</v>
+        <v>-10.67896344058969</v>
       </c>
       <c r="F12">
-        <v>-2.080356244066367</v>
+        <v>-0.9826567773902409</v>
       </c>
       <c r="G12">
-        <v>-10.54003722331202</v>
+        <v>-6.877403188575887</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>0.1213054664816844</v>
       </c>
       <c r="E13">
-        <v>-14.27967992136061</v>
+        <v>-11.57494466537731</v>
       </c>
       <c r="F13">
-        <v>-1.635294319359859</v>
+        <v>-0.4399402763025056</v>
       </c>
       <c r="G13">
-        <v>-9.853031459303278</v>
+        <v>-6.69342837695938</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>0.4005062665289118</v>
       </c>
       <c r="E14">
-        <v>-15.25098325431781</v>
+        <v>-12.85490425822332</v>
       </c>
       <c r="F14">
-        <v>-1.515434526379188</v>
+        <v>-0.1591585181843908</v>
       </c>
       <c r="G14">
-        <v>-9.686004157041305</v>
+        <v>-5.826129331923834</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>0.7769515624485244</v>
       </c>
       <c r="E15">
-        <v>-16.15309150443781</v>
+        <v>-13.36084348825628</v>
       </c>
       <c r="F15">
-        <v>-1.149419561084823</v>
+        <v>0.4847008144177614</v>
       </c>
       <c r="G15">
-        <v>-8.715080853936934</v>
+        <v>-6.360016891861084</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>1.231380303937907</v>
       </c>
       <c r="E16">
-        <v>-16.36967935927666</v>
+        <v>-13.73939221597947</v>
       </c>
       <c r="F16">
-        <v>-0.8797213588161659</v>
+        <v>0.1376115591751573</v>
       </c>
       <c r="G16">
-        <v>-8.341802526891385</v>
+        <v>-6.056589209372993</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>1.733209219720194</v>
       </c>
       <c r="E17">
-        <v>-17.38851808389238</v>
+        <v>-14.50126268302993</v>
       </c>
       <c r="F17">
-        <v>-0.6671042975396169</v>
+        <v>0.7334504334370221</v>
       </c>
       <c r="G17">
-        <v>-7.88724506059683</v>
+        <v>-4.365628084820957</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>2.242120492049134</v>
       </c>
       <c r="E18">
-        <v>-17.98195648870155</v>
+        <v>-16.22376286980151</v>
       </c>
       <c r="F18">
-        <v>-0.1564381596335972</v>
+        <v>0.9821114171441833</v>
       </c>
       <c r="G18">
-        <v>-8.08040729257978</v>
+        <v>-4.307560306883463</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>2.713156929522308</v>
       </c>
       <c r="E19">
-        <v>-18.59890673055854</v>
+        <v>-17.61081634445491</v>
       </c>
       <c r="F19">
-        <v>0.2192943836630082</v>
+        <v>1.111808901400502</v>
       </c>
       <c r="G19">
-        <v>-7.095817701680324</v>
+        <v>-3.403442674729388</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>3.105673370784503</v>
       </c>
       <c r="E20">
-        <v>-19.63528423500597</v>
+        <v>-18.32862475941074</v>
       </c>
       <c r="F20">
-        <v>0.5528315481958123</v>
+        <v>1.472667279612439</v>
       </c>
       <c r="G20">
-        <v>-6.683948927874145</v>
+        <v>-2.774104379627892</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>3.388341723060576</v>
       </c>
       <c r="E21">
-        <v>-20.81583023796158</v>
+        <v>-18.51495335093034</v>
       </c>
       <c r="F21">
-        <v>1.061207250233091</v>
+        <v>1.597714309269441</v>
       </c>
       <c r="G21">
-        <v>-6.678144446935487</v>
+        <v>-3.129913483090958</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>3.545310751925275</v>
       </c>
       <c r="E22">
-        <v>-20.47051598098069</v>
+        <v>-17.35257105721949</v>
       </c>
       <c r="F22">
-        <v>0.9616474288254243</v>
+        <v>1.84216387310077</v>
       </c>
       <c r="G22">
-        <v>-6.199309222322601</v>
+        <v>-3.235467099436735</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>3.578181113656866</v>
       </c>
       <c r="E23">
-        <v>-22.15737254883789</v>
+        <v>-18.54648964391976</v>
       </c>
       <c r="F23">
-        <v>0.8909611816097369</v>
+        <v>2.47908065850006</v>
       </c>
       <c r="G23">
-        <v>-6.526004046888714</v>
+        <v>-3.451099136658763</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>3.505101274792765</v>
       </c>
       <c r="E24">
-        <v>-22.53839382336927</v>
+        <v>-20.42694300407888</v>
       </c>
       <c r="F24">
-        <v>1.379232406781072</v>
+        <v>1.796505918593267</v>
       </c>
       <c r="G24">
-        <v>-6.197235490297031</v>
+        <v>-2.908480246151831</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>3.353301163471645</v>
       </c>
       <c r="E25">
-        <v>-21.88868460054079</v>
+        <v>-18.69028227908532</v>
       </c>
       <c r="F25">
-        <v>1.305900354080843</v>
+        <v>2.59647523009</v>
       </c>
       <c r="G25">
-        <v>-6.822652725634992</v>
+        <v>-2.054745771043029</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>3.155601223254132</v>
       </c>
       <c r="E26">
-        <v>-22.07885786649291</v>
+        <v>-19.85950256854775</v>
       </c>
       <c r="F26">
-        <v>1.322373268252914</v>
+        <v>2.846756500437037</v>
       </c>
       <c r="G26">
-        <v>-6.498586159537994</v>
+        <v>-2.995974019034424</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>2.946321725484438</v>
       </c>
       <c r="E27">
-        <v>-22.73686325370344</v>
+        <v>-20.62379576919231</v>
       </c>
       <c r="F27">
-        <v>1.121030287328466</v>
+        <v>2.353263247158454</v>
       </c>
       <c r="G27">
-        <v>-6.501700038797907</v>
+        <v>-3.295674233830986</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>2.756243296537562</v>
       </c>
       <c r="E28">
-        <v>-22.63885801922944</v>
+        <v>-19.60514724048492</v>
       </c>
       <c r="F28">
-        <v>1.057734734080556</v>
+        <v>2.278546164160744</v>
       </c>
       <c r="G28">
-        <v>-6.624640848187181</v>
+        <v>-4.055493585465361</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>2.608124034554816</v>
       </c>
       <c r="E29">
-        <v>-21.94481503586586</v>
+        <v>-19.60473062087621</v>
       </c>
       <c r="F29">
-        <v>1.335096991559914</v>
+        <v>2.14443513838231</v>
       </c>
       <c r="G29">
-        <v>-6.582926678501961</v>
+        <v>-4.178398301417482</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>2.513328107939208</v>
       </c>
       <c r="E30">
-        <v>-21.53374280781959</v>
+        <v>-19.63122672229509</v>
       </c>
       <c r="F30">
-        <v>0.9804579958081955</v>
+        <v>2.101934920414278</v>
       </c>
       <c r="G30">
-        <v>-6.905323102825202</v>
+        <v>-3.167545813156229</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>2.473053288885437</v>
       </c>
       <c r="E31">
-        <v>-22.15144477636185</v>
+        <v>-19.43584118276015</v>
       </c>
       <c r="F31">
-        <v>1.18379734217339</v>
+        <v>1.898557469148555</v>
       </c>
       <c r="G31">
-        <v>-6.964939617338753</v>
+        <v>-3.333234377021949</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>2.47907368709403</v>
       </c>
       <c r="E32">
-        <v>-21.34763611152636</v>
+        <v>-19.44603477775141</v>
       </c>
       <c r="F32">
-        <v>0.8666850465032946</v>
+        <v>2.002577220652894</v>
       </c>
       <c r="G32">
-        <v>-7.106393078766414</v>
+        <v>-2.942821510992979</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>2.518002211917903</v>
       </c>
       <c r="E33">
-        <v>-21.05486120998245</v>
+        <v>-19.16555015466433</v>
       </c>
       <c r="F33">
-        <v>0.9491241704299014</v>
+        <v>2.014040168772834</v>
       </c>
       <c r="G33">
-        <v>-7.356569816566276</v>
+        <v>-3.984051548451571</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>2.571390984775612</v>
       </c>
       <c r="E34">
-        <v>-21.01914060700995</v>
+        <v>-18.59579114044126</v>
       </c>
       <c r="F34">
-        <v>0.7033293379364265</v>
+        <v>2.152392435653601</v>
       </c>
       <c r="G34">
-        <v>-7.160415110521112</v>
+        <v>-3.824564493333201</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>2.617427712228772</v>
       </c>
       <c r="E35">
-        <v>-21.01336680265017</v>
+        <v>-18.08873790580241</v>
       </c>
       <c r="F35">
-        <v>0.9393891967122016</v>
+        <v>1.849196712350538</v>
       </c>
       <c r="G35">
-        <v>-6.864832828781654</v>
+        <v>-4.152735867601065</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>2.633081323163557</v>
       </c>
       <c r="E36">
-        <v>-20.66386823568619</v>
+        <v>-17.61908986646692</v>
       </c>
       <c r="F36">
-        <v>0.9313076443304896</v>
+        <v>2.006270082534575</v>
       </c>
       <c r="G36">
-        <v>-6.630993293126267</v>
+        <v>-3.264459973135988</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>2.596385395006955</v>
       </c>
       <c r="E37">
-        <v>-20.21054081667434</v>
+        <v>-19.2831999093836</v>
       </c>
       <c r="F37">
-        <v>0.8741386963936846</v>
+        <v>2.282422923605846</v>
       </c>
       <c r="G37">
-        <v>-6.7944801573256</v>
+        <v>-3.381720988005864</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>2.487423733340993</v>
       </c>
       <c r="E38">
-        <v>-20.31984006532347</v>
+        <v>-19.0853599369365</v>
       </c>
       <c r="F38">
-        <v>1.170381103717649</v>
+        <v>1.878938415580651</v>
       </c>
       <c r="G38">
-        <v>-6.951686763460155</v>
+        <v>-2.441381951057078</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>2.288357225143015</v>
       </c>
       <c r="E39">
-        <v>-19.3483193656139</v>
+        <v>-17.14927880206715</v>
       </c>
       <c r="F39">
-        <v>0.9277423510288405</v>
+        <v>2.069406589241147</v>
       </c>
       <c r="G39">
-        <v>-6.681766915537114</v>
+        <v>-3.140528234835761</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>1.989761155922196</v>
       </c>
       <c r="E40">
-        <v>-19.11309231175947</v>
+        <v>-16.63039266484626</v>
       </c>
       <c r="F40">
-        <v>1.082945267617356</v>
+        <v>2.270539164845284</v>
       </c>
       <c r="G40">
-        <v>-6.384668709437192</v>
+        <v>-3.01537916333698</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>1.591226136846917</v>
       </c>
       <c r="E41">
-        <v>-19.32141570153433</v>
+        <v>-15.58458234904086</v>
       </c>
       <c r="F41">
-        <v>0.958438333506979</v>
+        <v>2.17147139367488</v>
       </c>
       <c r="G41">
-        <v>-6.54729589358795</v>
+        <v>-2.726995881698944</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>1.101450736024129</v>
       </c>
       <c r="E42">
-        <v>-18.4449657851418</v>
+        <v>-16.42485881506013</v>
       </c>
       <c r="F42">
-        <v>1.087116925857854</v>
+        <v>2.070629259527679</v>
       </c>
       <c r="G42">
-        <v>-6.246401314143752</v>
+        <v>-3.085032934600873</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>0.5370822254939438</v>
       </c>
       <c r="E43">
-        <v>-18.20452645770454</v>
+        <v>-15.67498880412999</v>
       </c>
       <c r="F43">
-        <v>1.041478852168018</v>
+        <v>1.920674878803301</v>
       </c>
       <c r="G43">
-        <v>-6.714382257837994</v>
+        <v>-3.304546656927724</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-0.0756743898652123</v>
       </c>
       <c r="E44">
-        <v>-17.99124438889128</v>
+        <v>-15.54737640659384</v>
       </c>
       <c r="F44">
-        <v>0.9108221184592579</v>
+        <v>1.77864631738891</v>
       </c>
       <c r="G44">
-        <v>-6.314880408089363</v>
+        <v>-1.401087061742929</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-0.7060133267045441</v>
       </c>
       <c r="E45">
-        <v>-16.92040519724549</v>
+        <v>-14.66934152429862</v>
       </c>
       <c r="F45">
-        <v>0.967474165136716</v>
+        <v>1.930442987217113</v>
       </c>
       <c r="G45">
-        <v>-6.299514447526483</v>
+        <v>-1.888125340254426</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-1.323826912917813</v>
       </c>
       <c r="E46">
-        <v>-17.44802676082718</v>
+        <v>-15.51844398615884</v>
       </c>
       <c r="F46">
-        <v>0.6878960248548689</v>
+        <v>1.710047556028277</v>
       </c>
       <c r="G46">
-        <v>-6.101748661695631</v>
+        <v>-2.146186853461634</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-1.901446788023945</v>
       </c>
       <c r="E47">
-        <v>-16.64457584543829</v>
+        <v>-15.05132283531962</v>
       </c>
       <c r="F47">
-        <v>0.8827454337087715</v>
+        <v>2.130904585224982</v>
       </c>
       <c r="G47">
-        <v>-5.761574578963319</v>
+        <v>-2.187592588320268</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-2.415958834832799</v>
       </c>
       <c r="E48">
-        <v>-16.50328745639897</v>
+        <v>-14.3521173915873</v>
       </c>
       <c r="F48">
-        <v>0.8923213608851337</v>
+        <v>1.499657146330453</v>
       </c>
       <c r="G48">
-        <v>-6.139131618922384</v>
+        <v>-1.134435310493094</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-2.853901221303641</v>
       </c>
       <c r="E49">
-        <v>-15.71136603583361</v>
+        <v>-13.78980318863285</v>
       </c>
       <c r="F49">
-        <v>0.7152793660892122</v>
+        <v>1.747980156137272</v>
       </c>
       <c r="G49">
-        <v>-5.657428606666544</v>
+        <v>-1.875551699238634</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-3.213723229223909</v>
       </c>
       <c r="E50">
-        <v>-15.23756085735907</v>
+        <v>-11.28024063390614</v>
       </c>
       <c r="F50">
-        <v>0.6274989291493541</v>
+        <v>1.815949358271777</v>
       </c>
       <c r="G50">
-        <v>-5.798862380764849</v>
+        <v>-2.828530001634401</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-3.498207198600044</v>
       </c>
       <c r="E51">
-        <v>-15.19552756161988</v>
+        <v>-11.89795165939642</v>
       </c>
       <c r="F51">
-        <v>0.3967720997128023</v>
+        <v>1.691036524134028</v>
       </c>
       <c r="G51">
-        <v>-5.814933803963009</v>
+        <v>-2.179911248649607</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-3.713408027455025</v>
       </c>
       <c r="E52">
-        <v>-14.67244352899387</v>
+        <v>-11.77526171310661</v>
       </c>
       <c r="F52">
-        <v>0.4456341793343339</v>
+        <v>1.546716698483493</v>
       </c>
       <c r="G52">
-        <v>-5.31803217344382</v>
+        <v>-1.100021858777638</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-3.866733128868828</v>
       </c>
       <c r="E53">
-        <v>-14.32292684813386</v>
+        <v>-12.19013785931933</v>
       </c>
       <c r="F53">
-        <v>0.377466169023157</v>
+        <v>1.745220035951144</v>
       </c>
       <c r="G53">
-        <v>-6.054403915814404</v>
+        <v>-1.991047416909529</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-3.96643545185753</v>
       </c>
       <c r="E54">
-        <v>-14.09791150316673</v>
+        <v>-10.7434398535109</v>
       </c>
       <c r="F54">
-        <v>0.5228653573995402</v>
+        <v>1.266229839160774</v>
       </c>
       <c r="G54">
-        <v>-5.698640749453169</v>
+        <v>-1.601438450162623</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-4.017516462153566</v>
       </c>
       <c r="E55">
-        <v>-13.09216006843318</v>
+        <v>-11.73268047201249</v>
       </c>
       <c r="F55">
-        <v>0.5546249636228733</v>
+        <v>1.297621650257265</v>
       </c>
       <c r="G55">
-        <v>-6.187523074481075</v>
+        <v>-2.530805082216625</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-4.024431252362992</v>
       </c>
       <c r="E56">
-        <v>-13.97446077324363</v>
+        <v>-10.20092413891799</v>
       </c>
       <c r="F56">
-        <v>0.4520639671148636</v>
+        <v>1.564544821726544</v>
       </c>
       <c r="G56">
-        <v>-5.942127076493324</v>
+        <v>-1.919375694386578</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-3.992109607393936</v>
       </c>
       <c r="E57">
-        <v>-13.10202308482189</v>
+        <v>-10.36821955418335</v>
       </c>
       <c r="F57">
-        <v>0.5336556711884065</v>
+        <v>1.708665839200407</v>
       </c>
       <c r="G57">
-        <v>-6.438070590317155</v>
+        <v>-1.939358333683596</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-3.925051382026302</v>
       </c>
       <c r="E58">
-        <v>-12.05481347054812</v>
+        <v>-10.09623940528267</v>
       </c>
       <c r="F58">
-        <v>0.4730042666902323</v>
+        <v>1.396008503422568</v>
       </c>
       <c r="G58">
-        <v>-6.312754176518842</v>
+        <v>-2.860994407743547</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-3.827779398971312</v>
       </c>
       <c r="E59">
-        <v>-12.07010159879801</v>
+        <v>-9.78544117718824</v>
       </c>
       <c r="F59">
-        <v>0.4661163917359545</v>
+        <v>1.818563685795012</v>
       </c>
       <c r="G59">
-        <v>-6.471338895708365</v>
+        <v>-3.029196387323802</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-3.70318938487347</v>
       </c>
       <c r="E60">
-        <v>-13.03443561025741</v>
+        <v>-9.55606491175172</v>
       </c>
       <c r="F60">
-        <v>0.3564372341356887</v>
+        <v>1.755486821541441</v>
       </c>
       <c r="G60">
-        <v>-6.723175931617306</v>
+        <v>-2.231862829600296</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-3.552543699411766</v>
       </c>
       <c r="E61">
-        <v>-12.48825636019228</v>
+        <v>-8.005836933179935</v>
       </c>
       <c r="F61">
-        <v>0.7140890021313893</v>
+        <v>1.693220100607808</v>
       </c>
       <c r="G61">
-        <v>-6.711694937380809</v>
+        <v>-3.37607400570206</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-3.374178821616898</v>
       </c>
       <c r="E62">
-        <v>-12.51659102205828</v>
+        <v>-8.706618285866922</v>
       </c>
       <c r="F62">
-        <v>0.4801580475808089</v>
+        <v>1.794408492329379</v>
       </c>
       <c r="G62">
-        <v>-6.576958136485331</v>
+        <v>-3.297236095293282</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-3.166604243264523</v>
       </c>
       <c r="E63">
-        <v>-11.95367453206081</v>
+        <v>-6.871445137310495</v>
       </c>
       <c r="F63">
-        <v>0.3133571589856976</v>
+        <v>1.414888653267174</v>
       </c>
       <c r="G63">
-        <v>-7.214151676000138</v>
+        <v>-3.711349224646121</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-2.927964313658158</v>
       </c>
       <c r="E64">
-        <v>-11.58783723087715</v>
+        <v>-8.646570720525213</v>
       </c>
       <c r="F64">
-        <v>0.5238047260343148</v>
+        <v>1.435350984851127</v>
       </c>
       <c r="G64">
-        <v>-7.462622178589089</v>
+        <v>-5.01023062261699</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-2.657853309222307</v>
       </c>
       <c r="E65">
-        <v>-11.48582882538037</v>
+        <v>-9.613594645545165</v>
       </c>
       <c r="F65">
-        <v>0.3206666729480004</v>
+        <v>1.2617102666111</v>
       </c>
       <c r="G65">
-        <v>-7.691041136228273</v>
+        <v>-5.047859671460702</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-2.360026925485179</v>
       </c>
       <c r="E66">
-        <v>-11.24840999010623</v>
+        <v>-8.433691685898637</v>
       </c>
       <c r="F66">
-        <v>0.396859906657499</v>
+        <v>1.175911284498739</v>
       </c>
       <c r="G66">
-        <v>-7.642623430897108</v>
+        <v>-4.45288560975127</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-2.043088545675349</v>
       </c>
       <c r="E67">
-        <v>-10.99813481712431</v>
+        <v>-8.198790682172762</v>
       </c>
       <c r="F67">
-        <v>0.5495536983829347</v>
+        <v>1.373849675397681</v>
       </c>
       <c r="G67">
-        <v>-7.734812631831266</v>
+        <v>-5.241540336450045</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-1.719166236371703</v>
       </c>
       <c r="E68">
-        <v>-10.53318280533477</v>
+        <v>-8.489663624633444</v>
       </c>
       <c r="F68">
-        <v>0.5337227689480333</v>
+        <v>1.291476820863298</v>
       </c>
       <c r="G68">
-        <v>-8.039969518081184</v>
+        <v>-4.940019043687991</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-1.401582776288425</v>
       </c>
       <c r="E69">
-        <v>-11.61414313638771</v>
+        <v>-7.741876711746837</v>
       </c>
       <c r="F69">
-        <v>0.3219382169112977</v>
+        <v>1.45658535485449</v>
       </c>
       <c r="G69">
-        <v>-7.476816743055247</v>
+        <v>-5.35100516889468</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-1.105596332063679</v>
       </c>
       <c r="E70">
-        <v>-11.36697449657505</v>
+        <v>-7.512772154750778</v>
       </c>
       <c r="F70">
-        <v>0.464569001427525</v>
+        <v>0.9559880227294981</v>
       </c>
       <c r="G70">
-        <v>-7.744810513922894</v>
+        <v>-5.15180877046391</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-0.8443603826348401</v>
       </c>
       <c r="E71">
-        <v>-11.16285353067931</v>
+        <v>-8.169844676315732</v>
       </c>
       <c r="F71">
-        <v>0.1780184927163144</v>
+        <v>1.123089608691826</v>
       </c>
       <c r="G71">
-        <v>-8.220800919443741</v>
+        <v>-5.208025939441876</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-0.6288057073233</v>
       </c>
       <c r="E72">
-        <v>-11.29680126335219</v>
+        <v>-8.841788706521875</v>
       </c>
       <c r="F72">
-        <v>0.2625127961692668</v>
+        <v>1.02693603404447</v>
       </c>
       <c r="G72">
-        <v>-7.79470805017737</v>
+        <v>-5.531377199238915</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-0.467000152594201</v>
       </c>
       <c r="E73">
-        <v>-11.39748282596473</v>
+        <v>-7.981759036881152</v>
       </c>
       <c r="F73">
-        <v>0.1478062768014108</v>
+        <v>1.298556048687622</v>
       </c>
       <c r="G73">
-        <v>-7.870809421805571</v>
+        <v>-5.849501473091759</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-0.3669374859664008</v>
       </c>
       <c r="E74">
-        <v>-11.42975726021739</v>
+        <v>-8.183982572167679</v>
       </c>
       <c r="F74">
-        <v>0.05010779694783434</v>
+        <v>1.089484399895055</v>
       </c>
       <c r="G74">
-        <v>-7.416881950050429</v>
+        <v>-4.507997007063703</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-0.3336522309574683</v>
       </c>
       <c r="E75">
-        <v>-11.86355789930817</v>
+        <v>-7.833831904946591</v>
       </c>
       <c r="F75">
-        <v>0.194183254214544</v>
+        <v>1.014956184665184</v>
       </c>
       <c r="G75">
-        <v>-7.172329226003455</v>
+        <v>-4.212936439552196</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-0.3687074076642355</v>
       </c>
       <c r="E76">
-        <v>-12.40274518550545</v>
+        <v>-8.801784167138115</v>
       </c>
       <c r="F76">
-        <v>-0.01602491465466419</v>
+        <v>0.4681955939169812</v>
       </c>
       <c r="G76">
-        <v>-7.155893587212197</v>
+        <v>-4.810223762461037</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-0.4676753361664848</v>
       </c>
       <c r="E77">
-        <v>-11.85409338863214</v>
+        <v>-9.067967869308978</v>
       </c>
       <c r="F77">
-        <v>-0.02867325652800984</v>
+        <v>0.9426065757046749</v>
       </c>
       <c r="G77">
-        <v>-7.073361021327484</v>
+        <v>-4.430435491841549</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-0.6194645427706734</v>
       </c>
       <c r="E78">
-        <v>-12.21540674428213</v>
+        <v>-8.95841049764141</v>
       </c>
       <c r="F78">
-        <v>-0.1272415221545258</v>
+        <v>0.467626505511258</v>
       </c>
       <c r="G78">
-        <v>-6.973926883190072</v>
+        <v>-4.734722854378214</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-0.8052453299005573</v>
       </c>
       <c r="E79">
-        <v>-12.85662507834623</v>
+        <v>-9.607037415182058</v>
       </c>
       <c r="F79">
-        <v>-0.2009645642688762</v>
+        <v>0.287979295233532</v>
       </c>
       <c r="G79">
-        <v>-6.99810292364006</v>
+        <v>-4.569191789147347</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-1.004660646870778</v>
       </c>
       <c r="E80">
-        <v>-14.46055170170097</v>
+        <v>-9.753714688290501</v>
       </c>
       <c r="F80">
-        <v>-0.2460815948623513</v>
+        <v>0.5451625227806944</v>
       </c>
       <c r="G80">
-        <v>-6.555384104731982</v>
+        <v>-4.218721233161498</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-1.199532060995534</v>
       </c>
       <c r="E81">
-        <v>-13.60514107554807</v>
+        <v>-10.64202920658313</v>
       </c>
       <c r="F81">
-        <v>-0.3544328795159294</v>
+        <v>0.1360749376429642</v>
       </c>
       <c r="G81">
-        <v>-6.327385143452406</v>
+        <v>-4.735018164318564</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-1.374842145729407</v>
       </c>
       <c r="E82">
-        <v>-14.18393439541643</v>
+        <v>-10.38488433853158</v>
       </c>
       <c r="F82">
-        <v>-0.4406766949235943</v>
+        <v>0.2743733606425501</v>
       </c>
       <c r="G82">
-        <v>-6.068880665334674</v>
+        <v>-3.814185989540678</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-1.519640073764478</v>
       </c>
       <c r="E83">
-        <v>-14.56136459005973</v>
+        <v>-13.02439145490839</v>
       </c>
       <c r="F83">
-        <v>-0.7213863850776656</v>
+        <v>0.2207407131482961</v>
       </c>
       <c r="G83">
-        <v>-6.61797340597839</v>
+        <v>-4.337508016056515</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-1.62903471589114</v>
       </c>
       <c r="E84">
-        <v>-16.22054312478205</v>
+        <v>-13.13559719111475</v>
       </c>
       <c r="F84">
-        <v>-0.5812962033858244</v>
+        <v>0.3122438331963351</v>
       </c>
       <c r="G84">
-        <v>-6.402948394744858</v>
+        <v>-3.571382156584888</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-1.702980927856866</v>
       </c>
       <c r="E85">
-        <v>-16.64578947647234</v>
+        <v>-13.19628779976555</v>
       </c>
       <c r="F85">
-        <v>-0.775707405883646</v>
+        <v>0.1567973765913967</v>
       </c>
       <c r="G85">
-        <v>-6.208529454904641</v>
+        <v>-3.997872053659952</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-1.744974079913377</v>
       </c>
       <c r="E86">
-        <v>-17.40698972936967</v>
+        <v>-14.69289864608652</v>
       </c>
       <c r="F86">
-        <v>-0.4792844144658709</v>
+        <v>-0.1951254024465425</v>
       </c>
       <c r="G86">
-        <v>-6.062314940994225</v>
+        <v>-3.13775888383959</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-1.762122662419703</v>
       </c>
       <c r="E87">
-        <v>-18.57848784125796</v>
+        <v>-15.75281515842581</v>
       </c>
       <c r="F87">
-        <v>-0.8208327201511491</v>
+        <v>-0.03863934475109069</v>
       </c>
       <c r="G87">
-        <v>-5.73462262507404</v>
+        <v>-3.303230887082387</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-1.76485010796076</v>
       </c>
       <c r="E88">
-        <v>-19.57419512064249</v>
+        <v>-17.19012110914233</v>
       </c>
       <c r="F88">
-        <v>-0.9213302534587851</v>
+        <v>-0.08110642802301014</v>
       </c>
       <c r="G88">
-        <v>-5.92341755116137</v>
+        <v>-3.093882389146695</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-1.766646636539538</v>
       </c>
       <c r="E89">
-        <v>-20.95918361114839</v>
+        <v>-19.58133652415259</v>
       </c>
       <c r="F89">
-        <v>-1.373206328420721</v>
+        <v>-0.2501455653404857</v>
       </c>
       <c r="G89">
-        <v>-5.591551521417572</v>
+        <v>-2.857326002040088</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-1.782484972650708</v>
       </c>
       <c r="E90">
-        <v>-22.28604008081783</v>
+        <v>-19.66615484231625</v>
       </c>
       <c r="F90">
-        <v>-1.015713606966358</v>
+        <v>0.1076105769479676</v>
       </c>
       <c r="G90">
-        <v>-6.455467627025331</v>
+        <v>-4.129675442481287</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-1.82991240209671</v>
       </c>
       <c r="E91">
-        <v>-24.1001014835505</v>
+        <v>-20.85490644017377</v>
       </c>
       <c r="F91">
-        <v>-1.2388625314021</v>
+        <v>-0.5035622063071188</v>
       </c>
       <c r="G91">
-        <v>-5.533490305923198</v>
+        <v>-3.831271310200706</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-1.924929390873662</v>
       </c>
       <c r="E92">
-        <v>-26.26468941684689</v>
+        <v>-23.64826393248718</v>
       </c>
       <c r="F92">
-        <v>-1.409939452530462</v>
+        <v>-0.6405377265644339</v>
       </c>
       <c r="G92">
-        <v>-6.328110293417043</v>
+        <v>-3.552882629432738</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-2.080585484727123</v>
       </c>
       <c r="E93">
-        <v>-27.82092668042686</v>
+        <v>-26.29683252535334</v>
       </c>
       <c r="F93">
-        <v>-1.628143851938894</v>
+        <v>-0.4870221943754211</v>
       </c>
       <c r="G93">
-        <v>-5.78372938693269</v>
+        <v>-3.530268450445045</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-2.302949596229457</v>
       </c>
       <c r="E94">
-        <v>-29.28399059129901</v>
+        <v>-28.53491306332021</v>
       </c>
       <c r="F94">
-        <v>-1.630537833732985</v>
+        <v>-0.8335216520272319</v>
       </c>
       <c r="G94">
-        <v>-6.205786353680945</v>
+        <v>-3.735718857168116</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-2.59287779899498</v>
       </c>
       <c r="E95">
-        <v>-31.33198616855691</v>
+        <v>-31.87281502658197</v>
       </c>
       <c r="F95">
-        <v>-1.648403233509162</v>
+        <v>-1.00859793097631</v>
       </c>
       <c r="G95">
-        <v>-6.353536479281181</v>
+        <v>-4.568118829697409</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-2.944296835714045</v>
       </c>
       <c r="E96">
-        <v>-33.80724553267552</v>
+        <v>-33.30526645316227</v>
       </c>
       <c r="F96">
-        <v>-1.833577311098366</v>
+        <v>-1.100526003501985</v>
       </c>
       <c r="G96">
-        <v>-6.008086192281282</v>
+        <v>-4.691958693793971</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-3.341161820894575</v>
       </c>
       <c r="E97">
-        <v>-36.07003116059124</v>
+        <v>-35.22284877171028</v>
       </c>
       <c r="F97">
-        <v>-1.884342150644128</v>
+        <v>-1.437147179875412</v>
       </c>
       <c r="G97">
-        <v>-6.714785848089806</v>
+        <v>-4.701287206687472</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-3.766977785168359</v>
       </c>
       <c r="E98">
-        <v>-39.0662733453963</v>
+        <v>-37.79704623594847</v>
       </c>
       <c r="F98">
-        <v>-1.977048888528435</v>
+        <v>-1.104743221949638</v>
       </c>
       <c r="G98">
-        <v>-6.745127303849991</v>
+        <v>-4.513164931019829</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-4.19259138642221</v>
       </c>
       <c r="E99">
-        <v>-40.85135251447987</v>
+        <v>-41.33989108313836</v>
       </c>
       <c r="F99">
-        <v>-2.472743942363659</v>
+        <v>-1.805030113663089</v>
       </c>
       <c r="G99">
-        <v>-7.111603658602812</v>
+        <v>-5.073745228343161</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-4.601272329412555</v>
       </c>
       <c r="E100">
-        <v>-43.91354286625863</v>
+        <v>-42.64318137407189</v>
       </c>
       <c r="F100">
-        <v>-2.493930267057659</v>
+        <v>-1.6632094724668</v>
       </c>
       <c r="G100">
-        <v>-7.402073797152656</v>
+        <v>-5.098193610182584</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-4.951631121920991</v>
       </c>
       <c r="E101">
-        <v>-46.38125552844346</v>
+        <v>-45.53723627865686</v>
       </c>
       <c r="F101">
-        <v>-2.250373683286548</v>
+        <v>-2.058696921585368</v>
       </c>
       <c r="G101">
-        <v>-7.46763916635348</v>
+        <v>-5.425344524545459</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-5.24575561979555</v>
       </c>
       <c r="E102">
-        <v>-49.33734260210399</v>
+        <v>-48.65727335740959</v>
       </c>
       <c r="F102">
-        <v>-2.646059112214386</v>
+        <v>-2.393672960296835</v>
       </c>
       <c r="G102">
-        <v>-8.162756110057165</v>
+        <v>-4.624923337334516</v>
       </c>
     </row>
   </sheetData>
